--- a/AAII_Financials/Yearly/CBRL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CBRL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/CBRL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CBRL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>CBRL</t>
   </si>
@@ -656,211 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E7" s="2">
         <v>45135</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44771</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44407</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44043</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43679</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43315</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42944</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42580</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42216</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41852</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41488</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41124</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40753</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3470800</v>
+      </c>
+      <c r="E8" s="3">
         <v>3442800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3267800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2821400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2522800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3072000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3030400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2926300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2912400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2842300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2683700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2644600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2580200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2434400</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1127600</v>
+        <v>2359200</v>
       </c>
       <c r="E9" s="3">
-        <v>1049900</v>
+        <v>2336300</v>
       </c>
       <c r="F9" s="3">
-        <v>865300</v>
+        <v>2199000</v>
       </c>
       <c r="G9" s="3">
-        <v>779900</v>
+        <v>1848400</v>
       </c>
       <c r="H9" s="3">
-        <v>931100</v>
+        <v>1704900</v>
       </c>
       <c r="I9" s="3">
-        <v>935400</v>
+        <v>2009800</v>
       </c>
       <c r="J9" s="3">
+        <v>1991200</v>
+      </c>
+      <c r="K9" s="3">
         <v>891300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>928200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>924200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>872800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>854700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>827500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>772500</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2315200</v>
+        <v>1111600</v>
       </c>
       <c r="E10" s="3">
-        <v>2217900</v>
+        <v>1106500</v>
       </c>
       <c r="F10" s="3">
-        <v>1956200</v>
+        <v>1068800</v>
       </c>
       <c r="G10" s="3">
-        <v>1742900</v>
+        <v>973100</v>
       </c>
       <c r="H10" s="3">
-        <v>2140900</v>
+        <v>817900</v>
       </c>
       <c r="I10" s="3">
-        <v>2095000</v>
+        <v>1062100</v>
       </c>
       <c r="J10" s="3">
+        <v>1039200</v>
+      </c>
+      <c r="K10" s="3">
         <v>2035000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1984200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1918100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1810900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1789900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1752700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1662000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +891,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,9 +936,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,26 +984,29 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E14" s="3">
         <v>14000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-217700</v>
       </c>
-      <c r="G14" s="3">
-        <v>-46200</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>-47500</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1003,63 +1023,69 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5300</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>111700</v>
       </c>
       <c r="E15" s="3">
-        <v>96200</v>
+        <v>104500</v>
       </c>
       <c r="F15" s="3">
-        <v>100100</v>
+        <v>103600</v>
       </c>
       <c r="G15" s="3">
-        <v>109400</v>
+        <v>108600</v>
       </c>
       <c r="H15" s="3">
-        <v>100400</v>
+        <v>118200</v>
       </c>
       <c r="I15" s="3">
-        <v>86900</v>
+        <v>107500</v>
       </c>
       <c r="J15" s="3">
+        <v>93700</v>
+      </c>
+      <c r="K15" s="3">
         <v>79200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>71400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>66800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>62700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>60600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>58400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>57000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1074,98 +1100,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3322200</v>
+        <v>3398000</v>
       </c>
       <c r="E17" s="3">
+        <v>3308200</v>
+      </c>
+      <c r="F17" s="3">
         <v>3114800</v>
       </c>
-      <c r="F17" s="3">
-        <v>2454800</v>
-      </c>
       <c r="G17" s="3">
-        <v>2419200</v>
+        <v>2672500</v>
       </c>
       <c r="H17" s="3">
+        <v>2466600</v>
+      </c>
+      <c r="I17" s="3">
         <v>2789100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2736900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2613100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2631900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2587400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2475300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2443100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2389200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2267300</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>120600</v>
+        <v>72800</v>
       </c>
       <c r="E18" s="3">
+        <v>134600</v>
+      </c>
+      <c r="F18" s="3">
         <v>153000</v>
       </c>
-      <c r="F18" s="3">
-        <v>366700</v>
-      </c>
       <c r="G18" s="3">
-        <v>103600</v>
+        <v>148900</v>
       </c>
       <c r="H18" s="3">
+        <v>56200</v>
+      </c>
+      <c r="I18" s="3">
         <v>282800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>293600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>313200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>280500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>254900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>208400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>201500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>191000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>167200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1183,31 +1216,32 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-142400</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+        <v>142400</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1227,189 +1261,204 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>225100</v>
+        <v>184500</v>
       </c>
       <c r="E21" s="3">
+        <v>239100</v>
+      </c>
+      <c r="F21" s="3">
         <v>256600</v>
       </c>
-      <c r="F21" s="3">
-        <v>475300</v>
-      </c>
       <c r="G21" s="3">
-        <v>79300</v>
+        <v>257500</v>
       </c>
       <c r="H21" s="3">
+        <v>31900</v>
+      </c>
+      <c r="I21" s="3">
         <v>390400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>387300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>399500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>358700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>327800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>276800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>267600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>255400</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E22" s="3">
         <v>17000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>56100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>17600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>35700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>44700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>51500</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E23" s="3">
         <v>103600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>143400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>310600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-61200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>266400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>278400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>298900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>266400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>238200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>190800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>165800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>146300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>115700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E24" s="3">
         <v>4600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>56000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-28700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>43000</v>
       </c>
-      <c r="I24" s="3">
-        <v>61300</v>
-      </c>
       <c r="J24" s="3">
+        <v>30800</v>
+      </c>
+      <c r="K24" s="3">
         <v>97000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>77100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>74300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>58700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>48500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>43200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>30500</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1452,99 +1501,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E26" s="3">
         <v>99100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>131900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>254500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>223400</v>
       </c>
-      <c r="I26" s="3">
-        <v>217100</v>
-      </c>
       <c r="J26" s="3">
+        <v>247600</v>
+      </c>
+      <c r="K26" s="3">
         <v>201900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>189300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>163900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>132100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>117300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>103100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>85200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>99100</v>
+        <v>40900</v>
       </c>
       <c r="E27" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F27" s="3">
         <v>131900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>254500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-32500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>223400</v>
       </c>
-      <c r="I27" s="3">
-        <v>217100</v>
-      </c>
       <c r="J27" s="3">
+        <v>247600</v>
+      </c>
+      <c r="K27" s="3">
         <v>201900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>189300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>163900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>132100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>117300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>103100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>85200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1587,20 +1645,23 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1609,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>30500</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1629,12 +1690,15 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1677,9 +1741,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1722,32 +1789,35 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>142400</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+        <v>-142400</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1767,54 +1837,60 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E33" s="3">
         <v>99100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>131900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>254500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-32500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>223400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>247600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>201900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>189300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>163900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>132100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>117300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>103100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>85200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1857,104 +1933,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E35" s="3">
         <v>99100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>131900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>254500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-32500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>223400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>247600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>201900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>189300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>163900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>132100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>117300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>103100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>85200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E38" s="2">
         <v>45135</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44771</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44407</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44043</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43679</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43315</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42944</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42580</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42216</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41852</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41488</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41124</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40753</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1972,8 +2057,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1991,53 +2077,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E41" s="3">
         <v>25100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>144600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>437000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>114700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>161000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>151000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>265500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>119400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>121700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>152000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2060,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2080,189 +2170,204 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E43" s="3">
         <v>32500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>34700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>48500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>49000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>32200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>35600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>25700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20200</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E44" s="3">
         <v>189400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>213200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>138300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>139100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>155000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>156300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>156400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>152300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>153100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>165400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>146700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>143300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>141500</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>35300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>24200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>22200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>17900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>18300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>16300</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>19100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>20300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31900</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>278200</v>
+      </c>
+      <c r="E46" s="3">
         <v>282300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>317300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>353600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>643000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>242400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>306800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>358900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>355700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>456800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>329600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>302200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>337300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>245900</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2275,17 +2380,17 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>89100</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+      <c r="J47" s="3">
+        <v>6100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -2299,83 +2404,89 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1810700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1861300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1903100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1954300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1822000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1169000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1149100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1098100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1080200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1052600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2910400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2824200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2763900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1009200</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E49" s="3">
         <v>28100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>25900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26000</v>
       </c>
-      <c r="G49" s="3">
-        <v>25600</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
+      <c r="H49" s="3">
+        <v>25700</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
@@ -2386,8 +2497,8 @@
       <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2395,9 +2506,12 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2440,9 +2554,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2485,54 +2602,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E52" s="3">
         <v>46400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>48600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>57800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>53600</v>
       </c>
-      <c r="H52" s="3">
-        <v>80800</v>
-      </c>
       <c r="I52" s="3">
-        <v>71500</v>
+        <v>68300</v>
       </c>
       <c r="J52" s="3">
+        <v>65400</v>
+      </c>
+      <c r="K52" s="3">
         <v>65000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>61700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>66700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>118400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>178300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>59300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>55800</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2575,54 +2698,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2161500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2218100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2294900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2391700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2544300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1581200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1527400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1521900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1497700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1576200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1432200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1388300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1419000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1310900</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2640,8 +2769,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2659,208 +2789,221 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>162300</v>
+      </c>
+      <c r="E57" s="3">
         <v>165500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>169900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>135200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>103500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>132200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>122300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>118400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>132500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>133100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>98500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>110600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>101300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>99700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>49900</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>46400</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>54700</v>
       </c>
       <c r="G58" s="3">
-        <v>39400</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+        <v>50600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>85600</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>25000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>100</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>323400</v>
+        <v>153100</v>
       </c>
       <c r="E59" s="3">
-        <v>332300</v>
+        <v>187800</v>
       </c>
       <c r="F59" s="3">
-        <v>330000</v>
+        <v>201100</v>
       </c>
       <c r="G59" s="3">
-        <v>308200</v>
+        <v>191000</v>
       </c>
       <c r="H59" s="3">
-        <v>260300</v>
+        <v>181300</v>
       </c>
       <c r="I59" s="3">
-        <v>242300</v>
+        <v>167400</v>
       </c>
       <c r="J59" s="3">
+        <v>156300</v>
+      </c>
+      <c r="K59" s="3">
         <v>257400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>236300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>312500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>584300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>393000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>337800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>167300</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>454200</v>
+      </c>
+      <c r="E60" s="3">
         <v>489000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>502300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>465300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>451100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>392500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>364600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>375800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>368800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>445600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>344400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>316100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>319100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>267100</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>414900</v>
+        <v>1152600</v>
       </c>
       <c r="E61" s="3">
-        <v>423200</v>
+        <v>1117300</v>
       </c>
       <c r="F61" s="3">
-        <v>327300</v>
+        <v>1145400</v>
       </c>
       <c r="G61" s="3">
-        <v>910000</v>
+        <v>1075600</v>
       </c>
       <c r="H61" s="3">
-        <v>400000</v>
+        <v>1566500</v>
       </c>
       <c r="I61" s="3">
-        <v>400000</v>
+        <v>410500</v>
       </c>
       <c r="J61" s="3">
         <v>400000</v>
@@ -2872,65 +3015,71 @@
         <v>400000</v>
       </c>
       <c r="M61" s="3">
+        <v>400000</v>
+      </c>
+      <c r="N61" s="3">
         <v>375000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>400000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>525000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>550100</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>830400</v>
+        <v>21100</v>
       </c>
       <c r="E62" s="3">
-        <v>857900</v>
+        <v>53700</v>
       </c>
       <c r="F62" s="3">
-        <v>935500</v>
+        <v>55500</v>
       </c>
       <c r="G62" s="3">
-        <v>764800</v>
+        <v>88600</v>
       </c>
       <c r="H62" s="3">
-        <v>184000</v>
+        <v>52100</v>
       </c>
       <c r="I62" s="3">
-        <v>181000</v>
+        <v>129400</v>
       </c>
       <c r="J62" s="3">
+        <v>128800</v>
+      </c>
+      <c r="K62" s="3">
         <v>201600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>202400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>192300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>184200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>188200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>307100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>225600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2973,9 +3122,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3018,9 +3170,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3063,54 +3218,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1721300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1734300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1783400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1728100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2125900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>976500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>945600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>977400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>971200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1037900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>903600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>904300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1036300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1042800</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3128,8 +3289,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3172,9 +3334,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3217,9 +3382,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3262,9 +3430,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3307,54 +3478,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>427400</v>
+      </c>
+      <c r="E72" s="3">
         <v>479700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>511300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>663400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>438500</v>
       </c>
-      <c r="H72" s="3">
-        <v>561600</v>
-      </c>
       <c r="I72" s="3">
+        <v>561700</v>
+      </c>
+      <c r="J72" s="3">
         <v>532800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>492800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>488500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>485700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>493200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>438700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>374900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>298800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3397,9 +3574,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3442,9 +3622,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3487,54 +3670,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>440100</v>
+      </c>
+      <c r="E76" s="3">
         <v>483800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>511500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>663600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>418400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>604700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>581800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>544500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>526400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>538300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>528600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>484000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>382700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>268000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3577,104 +3766,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E80" s="2">
         <v>45135</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44771</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44407</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44043</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43679</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43315</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42944</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42580</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42216</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41852</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41488</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41124</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40753</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E81" s="3">
         <v>99100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>131900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>254500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-32500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>223400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>247600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>201900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>189300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>163900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>132100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>117300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>103100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>85200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3692,53 +3890,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>111700</v>
+      </c>
+      <c r="E83" s="3">
         <v>104500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>103600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>108600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>118200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>107500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>93700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>86300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>78200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>73000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>68400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>66100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>64500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3781,9 +3983,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3826,9 +4031,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3871,9 +4079,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3916,9 +4127,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3961,54 +4175,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E89" s="3">
         <v>250500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>205300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>301900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>161000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>362800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>330600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>320800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>271400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>334100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>177600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>208500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>219800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>138200</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4026,53 +4246,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-128300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-127000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-98300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-71400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-297300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-138300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-152200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-110600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-114000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-90900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-91600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-74400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-80900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4115,9 +4339,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4160,9 +4387,12 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4170,44 +4400,47 @@
         <v>-124300</v>
       </c>
       <c r="E94" s="3">
+        <v>-124300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-98500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>78300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-157200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-241600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-151200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-109600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-112500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-88600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-88800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-73400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-79500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4225,53 +4458,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-116100</v>
+        <v>116100</v>
       </c>
       <c r="E96" s="3">
-        <v>-114800</v>
+        <v>116100</v>
       </c>
       <c r="F96" s="3">
-        <v>-31700</v>
+        <v>114800</v>
       </c>
       <c r="G96" s="3">
-        <v>-94500</v>
+        <v>31700</v>
       </c>
       <c r="H96" s="3">
-        <v>-193500</v>
+        <v>94500</v>
       </c>
       <c r="I96" s="3">
-        <v>-207200</v>
+        <v>120900</v>
       </c>
       <c r="J96" s="3">
+        <v>116300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-196900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-255500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-95700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-71500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-45400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-22400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4314,9 +4551,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4359,9 +4599,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4404,77 +4647,83 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-57800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-146100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-206200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-672600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>396300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-199000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-225700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-201100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-273400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-99300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-91200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-165300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-40600</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4491,55 +4740,61 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-20000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-99500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-292400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-77800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-46300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-114500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>146100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-30200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>99700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
